--- a/data/trans_dic/Predimed_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,29; 82,17</t>
+          <t>75,02; 82,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,15; 80,5</t>
+          <t>74,7; 80,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,31; 80,5</t>
+          <t>76,09; 80,43</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,11; 94,17</t>
+          <t>83,98; 93,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,97; 85,09</t>
+          <t>80,71; 85,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,44; 91,28</t>
+          <t>83,35; 90,53</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,88; 85,62</t>
+          <t>78,89; 85,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,15; 91,9</t>
+          <t>74,58; 91,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,92; 89,44</t>
+          <t>78,01; 88,89</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,95; 85,23</t>
+          <t>80,28; 85,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,53; 84,89</t>
+          <t>78,52; 85,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,01; 84,06</t>
+          <t>80,0; 84,34</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,11; 87,88</t>
+          <t>82,05; 87,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,97; 85,12</t>
+          <t>79,16; 85,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,06; 85,18</t>
+          <t>81,18; 85,25</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>434219; 473890</t>
+          <t>432673; 473221</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>471097; 504623</t>
+          <t>468311; 501972</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>918523; 968966</t>
+          <t>915872; 968100</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>940963; 1053482</t>
+          <t>939530; 1048109</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>718433; 755032</t>
+          <t>716119; 755514</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1673890; 1831113</t>
+          <t>1672082; 1815998</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>506879; 550202</t>
+          <t>506912; 550156</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>656891; 814126</t>
+          <t>660653; 811861</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1190921; 1367046</t>
+          <t>1192267; 1358707</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>710220; 757086</t>
+          <t>713174; 757561</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>833736; 901246</t>
+          <t>833624; 902512</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1560200; 1639146</t>
+          <t>1559882; 1644629</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2649186; 2835376</t>
+          <t>2647321; 2829739</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2733822; 2946526</t>
+          <t>2740215; 2946594</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5421362; 5697167</t>
+          <t>5429194; 5701654</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,02; 82,05</t>
+          <t>74,7; 81,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,7; 80,07</t>
+          <t>75,2; 80,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,09; 80,43</t>
+          <t>75,62; 79,94</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,98; 93,69</t>
+          <t>81,59; 86,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,71; 85,15</t>
+          <t>80,86; 85,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,35; 90,53</t>
+          <t>81,95; 85,28</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,89; 85,62</t>
+          <t>79,32; 85,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,58; 91,65</t>
+          <t>79,29; 84,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,01; 88,89</t>
+          <t>80,21; 84,14</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,28; 85,28</t>
+          <t>80,14; 85,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,52; 85,01</t>
+          <t>78,38; 82,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,0; 84,34</t>
+          <t>80,0; 83,18</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,05; 87,71</t>
+          <t>80,74; 83,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,16; 85,12</t>
+          <t>79,84; 82,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,18; 85,25</t>
+          <t>80,7; 82,69</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>455829</t>
+          <t>491295</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>487420</t>
+          <t>527912</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>943250</t>
+          <t>1019207</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>432673; 473221</t>
+          <t>467652; 511350</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>468311; 501972</t>
+          <t>509475; 546234</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>915872; 968100</t>
+          <t>985713; 1042063</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>987271</t>
+          <t>818072</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>737432</t>
+          <t>824838</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1724702</t>
+          <t>1642910</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>939530; 1048109</t>
+          <t>791340; 840548</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>716119; 755514</t>
+          <t>803056; 845866</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1672082; 1815998</t>
+          <t>1608779; 1674085</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>531305</t>
+          <t>602386</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>739874</t>
+          <t>621025</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1271179</t>
+          <t>1223410</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>506912; 550156</t>
+          <t>578594; 624334</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>660653; 811861</t>
+          <t>600861; 639802</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1192267; 1358707</t>
+          <t>1192919; 1251361</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>735439</t>
+          <t>788064</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>861682</t>
+          <t>873592</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1597121</t>
+          <t>1661656</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>713174; 757561</t>
+          <t>762863; 812166</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>833624; 902512</t>
+          <t>848887; 894894</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1559882; 1644629</t>
+          <t>1627990; 1692754</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2709843</t>
+          <t>2699816</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2826408</t>
+          <t>2847367</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5536252</t>
+          <t>5547183</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2647321; 2829739</t>
+          <t>2645926; 2743604</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2740215; 2946594</t>
+          <t>2803606; 2885880</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5429194; 5701654</t>
+          <t>5478334; 5613500</t>
         </is>
       </c>
     </row>
